--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9a451fe83c4a40f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1d0c176ea9824471"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>0.7.0</x:v>
+        <x:v>0.8.0</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>
@@ -621,7 +621,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:v>4.2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="2" t="str">
         <x:v>首波倒计时秒数</x:v>
@@ -638,7 +638,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D21" s="2" t="str">
-        <x:v>4.8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="2" t="str">
         <x:v>波间倒计时秒数</x:v>
@@ -757,7 +757,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D28" s="2" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="2" t="str">
         <x:v>每关各道具免费数</x:v>
@@ -846,6 +846,23 @@
       </x:c>
       <x:c r="E33" s="2" t="str">
         <x:v>提示显示秒数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>challengeLevelId</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>挑战体验关内部ID，不计入冒险最大关卡</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1d0c176ea9824471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd76ac16479f24f30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>0.8.0</x:v>
+        <x:v>0.8.1</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>
@@ -863,6 +863,23 @@
       </x:c>
       <x:c r="E34" t="str">
         <x:v>挑战体验关内部ID，不计入冒险最大关卡</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>touchTravelTolerance</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>点击允许移动距离，390宽逻辑像素</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd76ac16479f24f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R98d6bc3598f04610"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>0.8.1</x:v>
+        <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R98d6bc3598f04610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R3816eedff7af4273"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>1.0.0</x:v>
+        <x:v>1.0.1</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R3816eedff7af4273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R02ef8c0ec9964345"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>1.0.1</x:v>
+        <x:v>1.1.0</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>
@@ -880,6 +880,108 @@
       </x:c>
       <x:c r="E35" t="str">
         <x:v>点击允许移动距离，390宽逻辑像素</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>hitFeedbackSeconds</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>受击形变秒数，真实时间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>hitFeedbackScale</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>受击形变幅度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>impactSeconds</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>命中特效秒数，真实时间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>impactLimit</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>命中特效并发上限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>bossEntranceSeconds</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>首领出场提示真实秒数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>bossDefeatSeconds</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>首领退场提示真实秒数</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R02ef8c0ec9964345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R88198fb5a06047c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>1.1.0</x:v>
+        <x:v>1.2.0</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>
@@ -982,6 +982,40 @@
       </x:c>
       <x:c r="E41" t="str">
         <x:v>首领退场提示真实秒数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>branchUnlockProgress</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>进化开放进度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>branchAdventureStartLevel</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>冒险进化起始关</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R88198fb5a06047c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R391f1ad8db2e46ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>1.2.0</x:v>
+        <x:v>1.3.0</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R391f1ad8db2e46ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R671cf2399f094588"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +60,11 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -57,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -77,6 +92,29 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -372,649 +410,649 @@
         <x:v>note</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="n">
+    <x:row r="6" ht="48" hidden="0" customHeight="1">
+      <x:c r="A6" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>gameName</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D6" s="2" t="str">
+      <x:c r="D6" s="15" t="str">
         <x:v>game.name</x:v>
       </x:c>
-      <x:c r="E6" s="2" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>游戏名I18键</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
+      <x:c r="A7" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="str">
+      <x:c r="B7" s="15" t="str">
         <x:v>maxLevels</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="str">
+      <x:c r="C7" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E7" s="2" t="str">
+      <x:c r="E7" s="15" t="str">
         <x:v>当前关卡上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="n">
+    <x:row r="8" ht="48" hidden="0" customHeight="1">
+      <x:c r="A8" s="14" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="str">
+      <x:c r="B8" s="15" t="str">
         <x:v>rewardAdUnitId</x:v>
       </x:c>
-      <x:c r="C8" s="2" t="str">
+      <x:c r="C8" s="15" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D8" s="2" t="str">
+      <x:c r="D8" s="15" t="str">
         <x:v>replace-with-douyin-ad-unit-id</x:v>
       </x:c>
-      <x:c r="E8" s="2" t="str">
+      <x:c r="E8" s="15" t="str">
         <x:v>抖音激励视频广告位</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+    <x:row r="9" ht="48" hidden="0" customHeight="1">
+      <x:c r="A9" s="14" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="2" t="str">
+      <x:c r="B9" s="15" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="C9" s="2" t="str">
+      <x:c r="C9" s="15" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D9" s="2" t="str">
-        <x:v>1.3.0</x:v>
-      </x:c>
-      <x:c r="E9" s="2" t="str">
+      <x:c r="D9" s="15" t="str">
+        <x:v>1.4.0</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="n">
+    <x:row r="10" ht="48" hidden="0" customHeight="1">
+      <x:c r="A10" s="14" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="2" t="str">
+      <x:c r="B10" s="15" t="str">
         <x:v>upgradeDamage</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="str">
+      <x:c r="C10" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
         <x:v>0.52</x:v>
       </x:c>
-      <x:c r="E10" s="2" t="str">
+      <x:c r="E10" s="15" t="str">
         <x:v>升级伤害增幅</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
+      <x:c r="A11" s="14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="str">
+      <x:c r="B11" s="15" t="str">
         <x:v>upgradeRange</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="str">
+      <x:c r="C11" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="E11" s="2" t="str">
+      <x:c r="E11" s="15" t="str">
         <x:v>升级射程增幅</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="n">
+    <x:row r="12" ht="48" hidden="0" customHeight="1">
+      <x:c r="A12" s="14" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="str">
+      <x:c r="B12" s="15" t="str">
         <x:v>upgradeRate</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="str">
+      <x:c r="C12" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="E12" s="2" t="str">
+      <x:c r="E12" s="15" t="str">
         <x:v>升级攻速增幅</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="7" t="n">
+    <x:row r="13" ht="48" hidden="0" customHeight="1">
+      <x:c r="A13" s="14" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="2" t="str">
+      <x:c r="B13" s="15" t="str">
         <x:v>upgradeCostBase</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="str">
+      <x:c r="C13" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="str">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E13" s="2" t="str">
+      <x:c r="E13" s="15" t="str">
         <x:v>升级费用基础比例</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="7" t="n">
+    <x:row r="14" ht="48" hidden="0" customHeight="1">
+      <x:c r="A14" s="14" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="2" t="str">
+      <x:c r="B14" s="15" t="str">
         <x:v>upgradeCostStep</x:v>
       </x:c>
-      <x:c r="C14" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="str">
+      <x:c r="C14" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="E14" s="2" t="str">
+      <x:c r="E14" s="15" t="str">
         <x:v>每级升级费用比例</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="7" t="n">
+    <x:row r="15" ht="48" hidden="0" customHeight="1">
+      <x:c r="A15" s="14" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="2" t="str">
+      <x:c r="B15" s="15" t="str">
         <x:v>maxStaffLevel</x:v>
       </x:c>
-      <x:c r="C15" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="str">
+      <x:c r="C15" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E15" s="2" t="str">
+      <x:c r="E15" s="15" t="str">
         <x:v>店员等级上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="7" t="n">
+    <x:row r="16" ht="48" hidden="0" customHeight="1">
+      <x:c r="A16" s="14" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="2" t="str">
+      <x:c r="B16" s="15" t="str">
         <x:v>sellRatio</x:v>
       </x:c>
-      <x:c r="C16" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="str">
+      <x:c r="C16" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="E16" s="2" t="str">
+      <x:c r="E16" s="15" t="str">
         <x:v>调岗返还比例</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="7" t="n">
+    <x:row r="17" ht="48" hidden="0" customHeight="1">
+      <x:c r="A17" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="2" t="str">
+      <x:c r="B17" s="15" t="str">
         <x:v>waveHealthGrowth</x:v>
       </x:c>
-      <x:c r="C17" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="str">
+      <x:c r="C17" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="E17" s="2" t="str">
+      <x:c r="E17" s="15" t="str">
         <x:v>逐波耐久增幅</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="7" t="n">
+    <x:row r="18" ht="48" hidden="0" customHeight="1">
+      <x:c r="A18" s="14" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="2" t="str">
+      <x:c r="B18" s="15" t="str">
         <x:v>waveBonusBase</x:v>
       </x:c>
-      <x:c r="C18" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="str">
+      <x:c r="C18" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E18" s="2" t="str">
+      <x:c r="E18" s="15" t="str">
         <x:v>波次奖励基础</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="7" t="n">
+    <x:row r="19" ht="48" hidden="0" customHeight="1">
+      <x:c r="A19" s="14" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B19" s="2" t="str">
+      <x:c r="B19" s="15" t="str">
         <x:v>waveBonusStep</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D19" s="2" t="str">
+      <x:c r="C19" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E19" s="2" t="str">
+      <x:c r="E19" s="15" t="str">
         <x:v>每波奖励增量</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="7" t="n">
+    <x:row r="20" ht="48" hidden="0" customHeight="1">
+      <x:c r="A20" s="14" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="2" t="str">
+      <x:c r="B20" s="15" t="str">
         <x:v>firstWaveDelay</x:v>
       </x:c>
-      <x:c r="C20" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D20" s="2" t="str">
+      <x:c r="C20" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E20" s="2" t="str">
+      <x:c r="E20" s="15" t="str">
         <x:v>首波倒计时秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="7" t="n">
+    <x:row r="21" ht="48" hidden="0" customHeight="1">
+      <x:c r="A21" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B21" s="2" t="str">
+      <x:c r="B21" s="15" t="str">
         <x:v>nextWaveDelay</x:v>
       </x:c>
-      <x:c r="C21" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D21" s="2" t="str">
+      <x:c r="C21" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E21" s="2" t="str">
+      <x:c r="E21" s="15" t="str">
         <x:v>波间倒计时秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="7" t="n">
+    <x:row r="22" ht="48" hidden="0" customHeight="1">
+      <x:c r="A22" s="14" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B22" s="2" t="str">
+      <x:c r="B22" s="15" t="str">
         <x:v>reviveWaveDelay</x:v>
       </x:c>
-      <x:c r="C22" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D22" s="2" t="str">
+      <x:c r="C22" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="str">
         <x:v>5.3</x:v>
       </x:c>
-      <x:c r="E22" s="2" t="str">
+      <x:c r="E22" s="15" t="str">
         <x:v>复活倒计时秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="7" t="n">
+    <x:row r="23" ht="48" hidden="0" customHeight="1">
+      <x:c r="A23" s="14" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B23" s="2" t="str">
+      <x:c r="B23" s="15" t="str">
         <x:v>reviveMinLives</x:v>
       </x:c>
-      <x:c r="C23" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D23" s="2" t="str">
+      <x:c r="C23" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E23" s="2" t="str">
+      <x:c r="E23" s="15" t="str">
         <x:v>复活最少耐久</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="7" t="n">
+    <x:row r="24" ht="48" hidden="0" customHeight="1">
+      <x:c r="A24" s="14" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B24" s="2" t="str">
+      <x:c r="B24" s="15" t="str">
         <x:v>reviveLifeRatio</x:v>
       </x:c>
-      <x:c r="C24" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D24" s="2" t="str">
+      <x:c r="C24" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="E24" s="2" t="str">
+      <x:c r="E24" s="15" t="str">
         <x:v>复活耐久比例</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="7" t="n">
+    <x:row r="25" ht="48" hidden="0" customHeight="1">
+      <x:c r="A25" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B25" s="2" t="str">
+      <x:c r="B25" s="15" t="str">
         <x:v>freezeSeconds</x:v>
       </x:c>
-      <x:c r="C25" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D25" s="2" t="str">
+      <x:c r="C25" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E25" s="2" t="str">
+      <x:c r="E25" s="15" t="str">
         <x:v>全场冻结秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="7" t="n">
+    <x:row r="26" ht="48" hidden="0" customHeight="1">
+      <x:c r="A26" s="14" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B26" s="2" t="str">
+      <x:c r="B26" s="15" t="str">
         <x:v>cashBase</x:v>
       </x:c>
-      <x:c r="C26" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D26" s="2" t="str">
+      <x:c r="C26" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="str">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E26" s="2" t="str">
+      <x:c r="E26" s="15" t="str">
         <x:v>零钱道具基础</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="7" t="n">
+    <x:row r="27" ht="48" hidden="0" customHeight="1">
+      <x:c r="A27" s="14" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B27" s="2" t="str">
+      <x:c r="B27" s="15" t="str">
         <x:v>cashPerLevel</x:v>
       </x:c>
-      <x:c r="C27" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D27" s="2" t="str">
+      <x:c r="C27" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E27" s="2" t="str">
+      <x:c r="E27" s="15" t="str">
         <x:v>零钱道具逐关增量</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="7" t="n">
+    <x:row r="28" ht="48" hidden="0" customHeight="1">
+      <x:c r="A28" s="14" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B28" s="2" t="str">
+      <x:c r="B28" s="15" t="str">
         <x:v>freePropCount</x:v>
       </x:c>
-      <x:c r="C28" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D28" s="2" t="str">
+      <x:c r="C28" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="2" t="str">
+      <x:c r="E28" s="15" t="str">
         <x:v>每关各道具免费数</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="7" t="n">
+    <x:row r="29" ht="48" hidden="0" customHeight="1">
+      <x:c r="A29" s="14" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B29" s="2" t="str">
+      <x:c r="B29" s="15" t="str">
         <x:v>slowSpeedRatio</x:v>
       </x:c>
-      <x:c r="C29" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D29" s="2" t="str">
+      <x:c r="C29" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
         <x:v>0.57</x:v>
       </x:c>
-      <x:c r="E29" s="2" t="str">
+      <x:c r="E29" s="15" t="str">
         <x:v>减速后的速度比例</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="7" t="n">
+    <x:row r="30" ht="48" hidden="0" customHeight="1">
+      <x:c r="A30" s="14" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B30" s="2" t="str">
+      <x:c r="B30" s="15" t="str">
         <x:v>markDamageRatio</x:v>
       </x:c>
-      <x:c r="C30" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D30" s="2" t="str">
+      <x:c r="C30" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="str">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="E30" s="2" t="str">
+      <x:c r="E30" s="15" t="str">
         <x:v>标记后的伤害倍率</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="7" t="n">
+    <x:row r="31" ht="48" hidden="0" customHeight="1">
+      <x:c r="A31" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B31" s="2" t="str">
+      <x:c r="B31" s="15" t="str">
         <x:v>musicVolume</x:v>
       </x:c>
-      <x:c r="C31" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D31" s="2" t="str">
+      <x:c r="C31" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="str">
         <x:v>0.32</x:v>
       </x:c>
-      <x:c r="E31" s="2" t="str">
+      <x:c r="E31" s="15" t="str">
         <x:v>音乐音量0至1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="7" t="n">
+    <x:row r="32" ht="48" hidden="0" customHeight="1">
+      <x:c r="A32" s="14" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B32" s="2" t="str">
+      <x:c r="B32" s="15" t="str">
         <x:v>maxEffectSources</x:v>
       </x:c>
-      <x:c r="C32" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D32" s="2" t="str">
+      <x:c r="C32" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E32" s="2" t="str">
+      <x:c r="E32" s="15" t="str">
         <x:v>音效并发上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="7" t="n">
+    <x:row r="33" ht="48" hidden="0" customHeight="1">
+      <x:c r="A33" s="14" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B33" s="2" t="str">
+      <x:c r="B33" s="15" t="str">
         <x:v>toastSeconds</x:v>
       </x:c>
-      <x:c r="C33" s="2" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D33" s="2" t="str">
+      <x:c r="C33" s="15" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="str">
         <x:v>2.3</x:v>
       </x:c>
-      <x:c r="E33" s="2" t="str">
+      <x:c r="E33" s="15" t="str">
         <x:v>提示显示秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="n">
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="16" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B34" t="str">
+      <x:c r="B34" s="16" t="str">
         <x:v>challengeLevelId</x:v>
       </x:c>
-      <x:c r="C34" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="C34" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="str">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E34" t="str">
+      <x:c r="E34" s="16" t="str">
         <x:v>挑战体验关内部ID，不计入冒险最大关卡</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="n">
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="16" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B35" t="str">
+      <x:c r="B35" s="16" t="str">
         <x:v>touchTravelTolerance</x:v>
       </x:c>
-      <x:c r="C35" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
+      <x:c r="C35" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E35" t="str">
+      <x:c r="E35" s="16" t="str">
         <x:v>点击允许移动距离，390宽逻辑像素</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="n">
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="16" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B36" t="str">
+      <x:c r="B36" s="16" t="str">
         <x:v>hitFeedbackSeconds</x:v>
       </x:c>
-      <x:c r="C36" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D36" t="n">
+      <x:c r="C36" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="E36" t="str">
+      <x:c r="E36" s="16" t="str">
         <x:v>受击形变秒数，真实时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="n">
+    <x:row r="37" ht="48" customHeight="1">
+      <x:c r="A37" s="16" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B37" t="str">
+      <x:c r="B37" s="16" t="str">
         <x:v>hitFeedbackScale</x:v>
       </x:c>
-      <x:c r="C37" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D37" t="n">
+      <x:c r="C37" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="n">
         <x:v>0.065</x:v>
       </x:c>
-      <x:c r="E37" t="str">
+      <x:c r="E37" s="16" t="str">
         <x:v>受击形变幅度</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="n">
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="16" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B38" t="str">
+      <x:c r="B38" s="16" t="str">
         <x:v>impactSeconds</x:v>
       </x:c>
-      <x:c r="C38" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D38" t="n">
+      <x:c r="C38" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="E38" t="str">
+      <x:c r="E38" s="16" t="str">
         <x:v>命中特效秒数，真实时间</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="n">
+    <x:row r="39" ht="48" customHeight="1">
+      <x:c r="A39" s="16" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B39" t="str">
+      <x:c r="B39" s="16" t="str">
         <x:v>impactLimit</x:v>
       </x:c>
-      <x:c r="C39" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D39" t="n">
+      <x:c r="C39" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E39" t="str">
+      <x:c r="E39" s="16" t="str">
         <x:v>命中特效并发上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="n">
+    <x:row r="40" ht="48" customHeight="1">
+      <x:c r="A40" s="16" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B40" t="str">
+      <x:c r="B40" s="16" t="str">
         <x:v>bossEntranceSeconds</x:v>
       </x:c>
-      <x:c r="C40" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D40" t="n">
+      <x:c r="C40" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="E40" t="str">
+      <x:c r="E40" s="16" t="str">
         <x:v>首领出场提示真实秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="n">
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="16" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B41" t="str">
+      <x:c r="B41" s="16" t="str">
         <x:v>bossDefeatSeconds</x:v>
       </x:c>
-      <x:c r="C41" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D41" t="n">
+      <x:c r="C41" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="n">
         <x:v>1.6</x:v>
       </x:c>
-      <x:c r="E41" t="str">
+      <x:c r="E41" s="16" t="str">
         <x:v>首领退场提示真实秒数</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="n">
+    <x:row r="42" ht="48" customHeight="1">
+      <x:c r="A42" s="16" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B42" t="str">
+      <x:c r="B42" s="16" t="str">
         <x:v>branchUnlockProgress</x:v>
       </x:c>
-      <x:c r="C42" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D42" t="n">
+      <x:c r="C42" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E42" t="str">
+      <x:c r="E42" s="16" t="str">
         <x:v>进化开放进度</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="n">
+    <x:row r="43" ht="48" customHeight="1">
+      <x:c r="A43" s="16" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B43" t="str">
+      <x:c r="B43" s="16" t="str">
         <x:v>branchAdventureStartLevel</x:v>
       </x:c>
-      <x:c r="C43" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="D43" t="n">
+      <x:c r="C43" s="16" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E43" t="str">
+      <x:c r="E43" s="16" t="str">
         <x:v>冒险进化起始关</x:v>
       </x:c>
     </x:row>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R671cf2399f094588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R5c5f8457ff694a14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.4.0</x:v>
+        <x:v>1.5.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R5c5f8457ff694a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R55bc2f8ff4d64e1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.5.0</x:v>
+        <x:v>1.5.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R55bc2f8ff4d64e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rab2ff6ed1c5a481f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.5.1</x:v>
+        <x:v>1.6.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rab2ff6ed1c5a481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R01ec20881bbd478f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.6.0</x:v>
+        <x:v>1.7.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -1054,6 +1054,23 @@
       </x:c>
       <x:c r="E43" s="16" t="str">
         <x:v>冒险进化起始关</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>battleGroundSkin</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>courtyard_ground</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>新版战场地面PNG资源键</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R01ec20881bbd478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9772a7b568cd4fe8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.7.0</x:v>
+        <x:v>1.7.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9772a7b568cd4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R2e4bae06ee774eac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.7.1</x:v>
+        <x:v>1.7.2</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R2e4bae06ee774eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9b33b173085444d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.7.2</x:v>
+        <x:v>1.7.3</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -930,7 +930,7 @@
       <x:c r="C36" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="n">
+      <x:c r="D36" s="16" t="str">
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
@@ -947,7 +947,7 @@
       <x:c r="C37" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="n">
+      <x:c r="D37" s="16" t="str">
         <x:v>0.065</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
@@ -964,7 +964,7 @@
       <x:c r="C38" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="n">
+      <x:c r="D38" s="16" t="str">
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
@@ -981,7 +981,7 @@
       <x:c r="C39" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D39" s="16" t="n">
+      <x:c r="D39" s="16" t="str">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
@@ -998,7 +998,7 @@
       <x:c r="C40" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="n">
+      <x:c r="D40" s="16" t="str">
         <x:v>2.4</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
@@ -1015,7 +1015,7 @@
       <x:c r="C41" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="n">
+      <x:c r="D41" s="16" t="str">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
@@ -1032,7 +1032,7 @@
       <x:c r="C42" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="n">
+      <x:c r="D42" s="16" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
@@ -1049,7 +1049,7 @@
       <x:c r="C43" s="16" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="D43" s="16" t="n">
+      <x:c r="D43" s="16" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
@@ -1071,6 +1071,74 @@
       </x:c>
       <x:c r="E44" t="str">
         <x:v>新版战场地面PNG资源键</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>staffLevelStarIcon</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>rank_star</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>店员等级星星独立PNG</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>staffLevelStarSize</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>等级星星逻辑尺寸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>staffLevelStarGap</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>等级星星中心间距</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>staffLevelStarOffsetY</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>等级星星相对塔位纵向偏移</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9b33b173085444d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd61659e84a7e495c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.7.3</x:v>
+        <x:v>1.7.4</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -1139,6 +1139,74 @@
       </x:c>
       <x:c r="E48" t="str">
         <x:v>等级星星相对塔位纵向偏移</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="36" customHeight="1">
+      <x:c r="A49" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>collectionScrollPadding</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>图鉴列表底部留白，逻辑像素</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="36" customHeight="1">
+      <x:c r="A50" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>collectionWheelScale</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>鼠标滚轮位移系数，与引擎滚动方向一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="36" customHeight="1">
+      <x:c r="A51" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>walletSaveKey</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>night_store_wallet_gold_v1</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>局外金币独立存储，不迁移战斗金币或收录数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="36" customHeight="1">
+      <x:c r="A52" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>walletInitialCoins</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>局外金币初始值；商品经营尚未实装</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd61659e84a7e495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9e1495bed04945a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.7.4</x:v>
+        <x:v>1.8.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9e1495bed04945a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rafff924e97514f51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.8.0</x:v>
+        <x:v>1.8.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rafff924e97514f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R8fb284dec4ef43bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.8.1</x:v>
+        <x:v>1.9.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -1207,6 +1207,23 @@
       </x:c>
       <x:c r="E52" t="str">
         <x:v>局外金币初始值；商品经营尚未实装</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>challengeProgressSaveKey</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>night_store_challenge_topics_v1</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>挑战专题通关记录，独立于冒险与经营存档</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R8fb284dec4ef43bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1de59784ce6c4557"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.9.0</x:v>
+        <x:v>1.9.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1de59784ce6c4557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9d562f0a7e9d44b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.9.1</x:v>
+        <x:v>1.10.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R9d562f0a7e9d44b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R77027cf6a59f439c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.10.0</x:v>
+        <x:v>1.10.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R77027cf6a59f439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Re4d326f4b2404040"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.10.1</x:v>
+        <x:v>1.11.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -1224,6 +1224,57 @@
       </x:c>
       <x:c r="E53" t="str">
         <x:v>挑战专题通关记录，独立于冒险与经营存档</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>rankingPreview</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>仅DEBUG展示明确标识的演示榜单，正式包禁用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>rankingAdventureWeight</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>每个冒险解锁进度的展示评分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>rankingChallengeWeight</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>每个已通关挑战专题的展示评分</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Re4d326f4b2404040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R4ff389ec43af4041"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.11.0</x:v>
+        <x:v>1.12.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R4ff389ec43af4041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Ra957d805a8734f16"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.12.0</x:v>
+        <x:v>1.13.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Ra957d805a8734f16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R20d64b97d94c4bab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.13.0</x:v>
+        <x:v>1.14.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R20d64b97d94c4bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rb5cc3bc1b6ab4f0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.14.0</x:v>
+        <x:v>1.15.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rb5cc3bc1b6ab4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd94dc09a6234486a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.15.0</x:v>
+        <x:v>1.16.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd94dc09a6234486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R5d1de216b9be4614"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.16.0</x:v>
+        <x:v>1.17.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R5d1de216b9be4614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rc653a8e9a80f4a60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.17.0</x:v>
+        <x:v>1.18.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rc653a8e9a80f4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R40715d28177d4bee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.18.0</x:v>
+        <x:v>1.19.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R40715d28177d4bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R7f9e064f2fc84bfb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.19.0</x:v>
+        <x:v>1.20.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R7f9e064f2fc84bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rcf4c0cf4096f4c7a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -438,7 +438,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
         <x:v>当前关卡上限</x:v>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.20.0</x:v>
+        <x:v>1.21.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -897,7 +897,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
         <x:v>挑战体验关内部ID，不计入冒险最大关卡</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rcf4c0cf4096f4c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rff6a7c7debb24406"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.21.0</x:v>
+        <x:v>1.22.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rff6a7c7debb24406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rccbdfe6586884698"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.22.0</x:v>
+        <x:v>1.23.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rccbdfe6586884698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R13cc747b122d4bc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.23.0</x:v>
+        <x:v>1.24.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R13cc747b122d4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1c19ce104d334660"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.24.0</x:v>
+        <x:v>1.24.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
@@ -1275,6 +1275,23 @@
       </x:c>
       <x:c r="E56" t="str">
         <x:v>每个已通关挑战专题的展示评分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>adventureClearedSaveKey</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>night_store_cleared_level_v1</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>仅正式冒险胜利写入；历史best到达记录不作为首通依据</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R1c19ce104d334660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R75c1584eb88c4036"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.24.1</x:v>
+        <x:v>1.25.0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>

--- a/design/tables/Global.xlsx
+++ b/design/tables/Global.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R75c1584eb88c4036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="R6d4391025fff40e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>1.25.0</x:v>
+        <x:v>1.25.1</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>客户端版本</x:v>
